--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/group_pdf_bins_gmprob.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/group_pdf_bins_gmprob.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -219,7 +220,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0.29499999999999998</v>
+        <v>0.29499999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -364,7 +365,7 @@
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>0.58499999999999996</v>
+        <v>0.58499999999999997</v>
       </c>
     </row>
     <row r="61">
@@ -489,7 +490,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.83499999999999996</v>
+        <v>0.83499999999999997</v>
       </c>
     </row>
     <row r="86">
